--- a/tasks/finalpool/canvas-arrange-exam/groundtruth_workspace/exam_schedule.xlsx
+++ b/tasks/finalpool/canvas-arrange-exam/groundtruth_workspace/exam_schedule.xlsx
@@ -1,52 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="宋体"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,360 +451,510 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.50390625" customWidth="1"/>
-    <col min="2" max="2" width="24.1640625" customWidth="1"/>
-    <col min="3" max="3" width="37.50390625" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" customWidth="1"/>
-    <col min="21" max="21" width="16.6640625" customWidth="1"/>
-    <col min="22" max="22" width="16.6640625" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" customWidth="1"/>
-    <col min="24" max="24" width="16.6640625" customWidth="1"/>
-    <col min="25" max="25" width="16.6640625" customWidth="1"/>
-    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+    <col width="16.85546875" customWidth="1" min="1" max="1"/>
+    <col width="20.0703125" customWidth="1" min="2" max="2"/>
+    <col width="31.42578125" customWidth="1" min="3" max="3"/>
+    <col width="20.5703125" customWidth="1" min="4" max="4"/>
+    <col width="7.35546875" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Course Code</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Course Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Proctor Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Open-book/Closed-book</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Final Date (MM/DD/YYYY)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Start Time (HH:MM)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Duration (minutes)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Location</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Information Source(Announcement/Email/Message)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Course Credit</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Course Code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Course Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Proctor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Open-book/Closed-book</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Final Date (MM/DD/YYYY)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Start Time (HH:MM)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Duration (minutes)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Information Source(Announcement/Email/Message)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Course Credit</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>NET101</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Network Programming</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Steven Hernandez</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Open-book</v>
-      </c>
-      <c r="E2" t="str">
-        <v>01/19/2025</v>
-      </c>
-      <c r="F2" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="G2" t="str">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NET101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Network Programming</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Steven Hernandez</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open-book</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>01/19/2025</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>120</v>
       </c>
-      <c r="H2" t="str">
-        <v>Building C Room 207</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Email</v>
-      </c>
-      <c r="J2" t="str">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Building C Room 207</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>MATH201</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Advanced Mathematics</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Christopher Thompson</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Open-book</v>
-      </c>
-      <c r="E3" t="str">
-        <v>01/20/2025</v>
-      </c>
-      <c r="F3" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MATH201</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Advanced Mathematics</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Christopher Thompson</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open-book</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>01/20/2025</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>150</v>
       </c>
-      <c r="H3" t="str">
-        <v>Building B Room 301</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Announcement</v>
-      </c>
-      <c r="J3" t="str">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Building B Room 301</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Announcement</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>MATH101</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Linear Algebra</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Christopher Thompson</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Closed-book</v>
-      </c>
-      <c r="E4" t="str">
-        <v>01/20/2025</v>
-      </c>
-      <c r="F4" t="str">
-        <v>14:00</v>
-      </c>
-      <c r="G4" t="str">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MATH101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Linear Algebra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Christopher Thompson</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed-book</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>01/20/2025</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>120</v>
       </c>
-      <c r="H4" t="str">
-        <v>Building C Room 101</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Announcement</v>
-      </c>
-      <c r="J4" t="str">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Building C Room 101</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Announcement</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>DB101</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Database Systems Fundamentals</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Steven Hernandez</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Closed-book</v>
-      </c>
-      <c r="E5" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="F5" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="G5" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="H5" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Announcement</v>
-      </c>
-      <c r="J5" t="str">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DB101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Database Systems Fundamentals</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Steven Hernandez</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed-book</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Announcement</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>CS401</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Software Engineering</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Debra Flores</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Closed-book</v>
-      </c>
-      <c r="E6" t="str">
-        <v>01/17/2025</v>
-      </c>
-      <c r="F6" t="str">
-        <v>14:00</v>
-      </c>
-      <c r="G6" t="str">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CS401</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Debra Flores</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed-book</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>01/17/2025</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>180</v>
       </c>
-      <c r="H6" t="str">
-        <v>Building C Room 301</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Announcement</v>
-      </c>
-      <c r="J6" t="str">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Building C Room 301</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Announcement</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>CS302</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Software Engineering Practice</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Debra Flores</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Closed-book</v>
-      </c>
-      <c r="E7" t="str">
-        <v>01/17/2025</v>
-      </c>
-      <c r="F7" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="G7" t="str">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CS302</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Software Engineering Practice</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Debra Flores</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed-book</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>01/17/2025</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>120</v>
       </c>
-      <c r="H7" t="str">
-        <v>Building C Room 305</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Announcement</v>
-      </c>
-      <c r="J7" t="str">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Building C Room 305</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Announcement</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>CS301</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Database Systems</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Black Smith</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Closed-book</v>
-      </c>
-      <c r="E8" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="F8" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="G8" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="H8" t="str">
-        <v>TBD</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Announcement</v>
-      </c>
-      <c r="J8" t="str">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CS301</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Database Systems</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed-book</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Announcement</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>CS201</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Data Structures and Algorithms</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Debra Flores</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Closed-book</v>
-      </c>
-      <c r="E9" t="str">
-        <v>01/16/2025</v>
-      </c>
-      <c r="F9" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="G9" t="str">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CS201</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data Structures and Algorithms</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Debra Flores</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed-book</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>01/16/2025</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>150</v>
       </c>
-      <c r="H9" t="str">
-        <v>Building B Room 203</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Announcement</v>
-      </c>
-      <c r="J9" t="str">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Building B Room 203</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Announcement</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>AI101</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Fundamentals of Artificial Intelligence</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Steven Hernandez</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Closed-book</v>
-      </c>
-      <c r="E10" t="str">
-        <v>01/18/2025</v>
-      </c>
-      <c r="F10" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="G10" t="str">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fundamentals of Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Steven Hernandez</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed-book</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>01/18/2025</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>120</v>
       </c>
-      <c r="H10" t="str">
-        <v>Building A Room 201</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Announcement</v>
-      </c>
-      <c r="J10" t="str">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Building A Room 201</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Announcement</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>